--- a/models/role.xlsx
+++ b/models/role.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/ymq/py/rbac/models/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F3E20885-988D-124E-AE50-B3093B45A23D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{723C9986-9ECF-E646-8DAB-891FA96A9BBC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="15100" yWindow="4360" windowWidth="27040" windowHeight="15820" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -16,16 +16,17 @@
     <sheet name="summary" sheetId="1" r:id="rId1"/>
     <sheet name="fields" sheetId="2" r:id="rId2"/>
     <sheet name="validation" sheetId="3" r:id="rId3"/>
-    <sheet name="codes" sheetId="6" r:id="rId4"/>
-    <sheet name="coding" sheetId="4" r:id="rId5"/>
-    <sheet name="help" sheetId="5" r:id="rId6"/>
+    <sheet name="data" sheetId="7" r:id="rId4"/>
+    <sheet name="codes" sheetId="6" r:id="rId5"/>
+    <sheet name="coding" sheetId="4" r:id="rId6"/>
+    <sheet name="help" sheetId="5" r:id="rId7"/>
   </sheets>
   <calcPr calcId="144525"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="108" uniqueCount="82">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="114" uniqueCount="85">
   <si>
     <t>name</t>
   </si>
@@ -273,6 +274,18 @@
   </si>
   <si>
     <t>appcodes_kv</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>role-01</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>owner</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>superuser</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
 </sst>
@@ -898,6 +911,39 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{33F5901B-2652-8B40-865E-C02C0AFE91D4}">
+  <dimension ref="A1:C2"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14"/>
+  <sheetData>
+    <row r="1" spans="1:3">
+      <c r="A1" t="s">
+        <v>66</v>
+      </c>
+      <c r="B1" s="9" t="s">
+        <v>73</v>
+      </c>
+      <c r="C1" s="9" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3">
+      <c r="A2" s="7" t="s">
+        <v>82</v>
+      </c>
+      <c r="B2" s="7" t="s">
+        <v>83</v>
+      </c>
+      <c r="C2" s="7" t="s">
+        <v>84</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="3" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3A004FF0-5960-3F4D-ADD8-9B74C235A6A8}">
   <dimension ref="A1:E2"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14"/>
@@ -945,7 +991,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="A1:D13"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="14"/>
@@ -1073,7 +1119,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
   <dimension ref="A1:E12"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="14"/>
